--- a/static/data/Vocab_Game.xlsx
+++ b/static/data/Vocab_Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ACA0A008A5DDF25F/course_app/static/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="8_{02FE82B8-B278-43D8-9221-81C7D10E9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCB5B2DE-ECC0-4D08-815C-BFEC31E492A2}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="8_{02FE82B8-B278-43D8-9221-81C7D10E9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1D641A-308A-4C72-AA12-28C419FF747A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7F57B12B-D2C6-49E8-96B6-3D12CF79857F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{7F57B12B-D2C6-49E8-96B6-3D12CF79857F}"/>
   </bookViews>
   <sheets>
     <sheet name="sets" sheetId="9" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3876" uniqueCount="3283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="3283">
   <si>
     <t>house</t>
   </si>
@@ -21119,6 +21119,9 @@
       <c r="B4" t="s">
         <v>1338</v>
       </c>
+      <c r="C4" t="s">
+        <v>2397</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
